--- a/output/07_Aviat_Ceragon_구성가격비교.xlsx
+++ b/output/07_Aviat_Ceragon_구성가격비교.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'직접대응_품목'!$A$1:$K$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'판매가_비교'!$A$1:$E$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'매입가_비교'!$A$1:$E$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'비교불가'!$A$1:$C$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'비교불가'!$A$1:$C$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'공급사확인사항'!$A$1:$B$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'요약'!$A$1:$B$5</definedName>
   </definedNames>
@@ -58,17 +58,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
   </fills>
@@ -100,7 +100,7 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -112,10 +112,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -487,14 +487,14 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -558,7 +558,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>4GHz(WBX 근거) 또는 미상(계약서 텍스트 근거만 있음, 발주이력 없음)</t>
+          <t>8GHz 2+0: 04v2 재분석 결과 참고후보 21건만 확인(반복 관측으로 뒷받침되는 유력 후보 없음)</t>
         </is>
       </c>
       <c r="C2" s="3" t="n"/>
@@ -583,12 +583,12 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>아니오</t>
+          <t>보류(대역 겹침, Aviat 근거 부족)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Aviat 2+0 구성의 발주이력 근거는 4GHz 대역(WBX) 위주이며 8GHz 대역 자체 수량 근거가 없음(계약서 텍스트로 존재만 확인). Ceragon은 8GHz/SD 데이터가 있으나 대역이 달라 동일 링크 총액으로 합산 비교하지 않음.</t>
+          <t>대역(8GHz)은 Aviat·Ceragon 양측에 모두 존재함(대역 자체는 겹침). 다만 04v2 재분석에서 2+0 구성 품목 대부분이 다중대역 혼재 윈도우 등으로 인해 '참고 후보' 수준에 그쳐, 총액을 산출할 만큼의 근거가 아직 없음. 임의로 수량을 채워 총액을 계산하지 않는다(공급사 확인 필요).</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>4GHz(WBX 근거) 또는 미상(계약서 텍스트 근거만 있음, 발주이력 없음)</t>
+          <t>8GHz 2+0: 04v2 재분석 결과 참고후보 21건만 확인(반복 관측으로 뒷받침되는 유력 후보 없음)</t>
         </is>
       </c>
       <c r="C3" s="3" t="n"/>
@@ -625,12 +625,12 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>아니오</t>
+          <t>보류(대역 겹침, Aviat 근거 부족)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Aviat 2+0 구성의 발주이력 근거는 4GHz 대역(WBX) 위주이며 8GHz 대역 자체 수량 근거가 없음(계약서 텍스트로 존재만 확인). Ceragon은 8GHz/Non_SD 데이터가 있으나 대역이 달라 동일 링크 총액으로 합산 비교하지 않음.</t>
+          <t>대역(8GHz)은 Aviat·Ceragon 양측에 모두 존재함(대역 자체는 겹침). 다만 04v2 재분석에서 2+0 구성 품목 대부분이 다중대역 혼재 윈도우 등으로 인해 '참고 후보' 수준에 그쳐, 총액을 산출할 만큼의 근거가 아직 없음. 임의로 수량을 채워 총액을 계산하지 않는다(공급사 확인 필요).</t>
         </is>
       </c>
     </row>
@@ -642,10 +642,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>4GHz(WBX 근거) 또는 미상(계약서 텍스트 근거만 있음, 발주이력 없음)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n"/>
+          <t>11GHz 2+0: 04v2 재분석 결과 유력후보 6건/참고후보 39건(표준 BoM 확정 아님)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>9544236</v>
+      </c>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -667,12 +669,12 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>아니오</t>
+          <t>보류(대역 겹침, Aviat 미확정)</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Aviat 2+0 구성의 발주이력 근거는 4GHz 대역(WBX) 위주이며 11GHz 대역 자체 수량 근거가 없음(계약서 텍스트로 존재만 확인). Ceragon은 11GHz/SD 데이터가 있으나 대역이 달라 동일 링크 총액으로 합산 비교하지 않음.</t>
+          <t>대역(11GHz)은 Aviat·Ceragon 양측에 모두 존재함(대역 자체는 겹침). 04v2 재분석에서 2+0 구성의 핵심 품목 6건이 '유력 후보' 수준까지 확인되었으나(반복 관측 비율 안정), 전체 품목(45건) 중 다수는 아직 참고 후보 단계이고 완성된 표준 BoM으로 확정되지 않아, 구성 총액 단위의 전면 비교는 보류한다. 왼쪽 '판매총액' 값은 유력후보 품목만의 부분 합계(참고용)이며 Ceragon 쪽 전체 품목 총액과 직접 비교 가능한 값이 아니다.</t>
         </is>
       </c>
     </row>
@@ -684,10 +686,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>4GHz(WBX 근거) 또는 미상(계약서 텍스트 근거만 있음, 발주이력 없음)</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n"/>
+          <t>11GHz 2+0: 04v2 재분석 결과 유력후보 6건/참고후보 39건(표준 BoM 확정 아님)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>9544236</v>
+      </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -709,12 +713,12 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>아니오</t>
+          <t>보류(대역 겹침, Aviat 미확정)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Aviat 2+0 구성의 발주이력 근거는 4GHz 대역(WBX) 위주이며 11GHz 대역 자체 수량 근거가 없음(계약서 텍스트로 존재만 확인). Ceragon은 11GHz/Non_SD 데이터가 있으나 대역이 달라 동일 링크 총액으로 합산 비교하지 않음.</t>
+          <t>대역(11GHz)은 Aviat·Ceragon 양측에 모두 존재함(대역 자체는 겹침). 04v2 재분석에서 2+0 구성의 핵심 품목 6건이 '유력 후보' 수준까지 확인되었으나(반복 관측 비율 안정), 전체 품목(45건) 중 다수는 아직 참고 후보 단계이고 완성된 표준 BoM으로 확정되지 않아, 구성 총액 단위의 전면 비교는 보류한다. 왼쪽 '판매총액' 값은 유력후보 품목만의 부분 합계(참고용)이며 Ceragon 쪽 전체 품목 총액과 직접 비교 가능한 값이 아니다.</t>
         </is>
       </c>
     </row>
@@ -726,7 +730,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>4GHz(WBX 근거) 또는 미상(계약서 텍스트 근거만 있음, 발주이력 없음)</t>
+          <t>8GHz 4+0: 04v2 재분석 결과 참고후보 13건만 확인(반복 관측으로 뒷받침되는 유력 후보 없음)</t>
         </is>
       </c>
       <c r="C6" s="3" t="n"/>
@@ -751,12 +755,12 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>아니오</t>
+          <t>보류(대역 겹침, Aviat 근거 부족)</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Aviat 4+0 구성의 발주이력 근거는 4GHz 대역(WBX) 위주이며 8GHz 대역 자체 수량 근거가 없음(계약서 텍스트로 존재만 확인). Ceragon은 8GHz/SD 데이터가 있으나 대역이 달라 동일 링크 총액으로 합산 비교하지 않음.</t>
+          <t>대역(8GHz)은 Aviat·Ceragon 양측에 모두 존재함(대역 자체는 겹침). 다만 04v2 재분석에서 4+0 구성 품목 대부분이 다중대역 혼재 윈도우 등으로 인해 '참고 후보' 수준에 그쳐, 총액을 산출할 만큼의 근거가 아직 없음. 임의로 수량을 채워 총액을 계산하지 않는다(공급사 확인 필요).</t>
         </is>
       </c>
     </row>
@@ -768,7 +772,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>4GHz(WBX 근거) 또는 미상(계약서 텍스트 근거만 있음, 발주이력 없음)</t>
+          <t>8GHz 4+0: 04v2 재분석 결과 참고후보 13건만 확인(반복 관측으로 뒷받침되는 유력 후보 없음)</t>
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
@@ -793,12 +797,12 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>아니오</t>
+          <t>보류(대역 겹침, Aviat 근거 부족)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Aviat 4+0 구성의 발주이력 근거는 4GHz 대역(WBX) 위주이며 8GHz 대역 자체 수량 근거가 없음(계약서 텍스트로 존재만 확인). Ceragon은 8GHz/Non_SD 데이터가 있으나 대역이 달라 동일 링크 총액으로 합산 비교하지 않음.</t>
+          <t>대역(8GHz)은 Aviat·Ceragon 양측에 모두 존재함(대역 자체는 겹침). 다만 04v2 재분석에서 4+0 구성 품목 대부분이 다중대역 혼재 윈도우 등으로 인해 '참고 후보' 수준에 그쳐, 총액을 산출할 만큼의 근거가 아직 없음. 임의로 수량을 채워 총액을 계산하지 않는다(공급사 확인 필요).</t>
         </is>
       </c>
     </row>
@@ -810,7 +814,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>4GHz(WBX 근거) 또는 미상(계약서 텍스트 근거만 있음, 발주이력 없음)</t>
+          <t>11GHz 4+0: 04v2 재분석 결과 참고후보 17건만 확인(반복 관측으로 뒷받침되는 유력 후보 없음)</t>
         </is>
       </c>
       <c r="C8" s="3" t="n"/>
@@ -835,12 +839,12 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>아니오</t>
+          <t>보류(대역 겹침, Aviat 근거 부족)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Aviat 4+0 구성의 발주이력 근거는 4GHz 대역(WBX) 위주이며 11GHz 대역 자체 수량 근거가 없음(계약서 텍스트로 존재만 확인). Ceragon은 11GHz/SD 데이터가 있으나 대역이 달라 동일 링크 총액으로 합산 비교하지 않음.</t>
+          <t>대역(11GHz)은 Aviat·Ceragon 양측에 모두 존재함(대역 자체는 겹침). 다만 04v2 재분석에서 4+0 구성 품목 대부분이 다중대역 혼재 윈도우 등으로 인해 '참고 후보' 수준에 그쳐, 총액을 산출할 만큼의 근거가 아직 없음. 임의로 수량을 채워 총액을 계산하지 않는다(공급사 확인 필요).</t>
         </is>
       </c>
     </row>
@@ -852,7 +856,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>4GHz(WBX 근거) 또는 미상(계약서 텍스트 근거만 있음, 발주이력 없음)</t>
+          <t>11GHz 4+0: 04v2 재분석 결과 참고후보 17건만 확인(반복 관측으로 뒷받침되는 유력 후보 없음)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n"/>
@@ -877,12 +881,12 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>아니오</t>
+          <t>보류(대역 겹침, Aviat 근거 부족)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Aviat 4+0 구성의 발주이력 근거는 4GHz 대역(WBX) 위주이며 11GHz 대역 자체 수량 근거가 없음(계약서 텍스트로 존재만 확인). Ceragon은 11GHz/Non_SD 데이터가 있으나 대역이 달라 동일 링크 총액으로 합산 비교하지 않음.</t>
+          <t>대역(11GHz)은 Aviat·Ceragon 양측에 모두 존재함(대역 자체는 겹침). 다만 04v2 재분석에서 4+0 구성 품목 대부분이 다중대역 혼재 윈도우 등으로 인해 '참고 후보' 수준에 그쳐, 총액을 산출할 만큼의 근거가 아직 없음. 임의로 수량을 채워 총액을 계산하지 않는다(공급사 확인 필요).</t>
         </is>
       </c>
     </row>
@@ -894,7 +898,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>4GHz(WBX 근거) 또는 미상(계약서 텍스트 근거만 있음, 발주이력 없음)</t>
+          <t>8GHz 자체는 Aviat 자료에도 존재하나, 6+0 배수를 시사하는 발주이력 근거가 확인되지 않음(04v2 확인필요 시트 참조)</t>
         </is>
       </c>
       <c r="C10" s="3" t="n"/>
@@ -917,14 +921,14 @@
           <t>Ceragon 매입가 미제공</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>아니오</t>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>아니오(근거 없음)</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Aviat 6+0 구성의 발주이력 근거는 4GHz 대역(WBX) 위주이며 8GHz 대역 자체 수량 근거가 없음(계약서 텍스트로 존재만 확인). Ceragon은 8GHz/SD 데이터가 있으나 대역이 달라 동일 링크 총액으로 합산 비교하지 않음.</t>
+          <t>대역(8GHz)은 Aviat·Ceragon 양측 자료에 모두 존재하므로 '대역이 겹치지 않는다'고 표현하지 않는다. 다만 6+0 구성 자체를 시사하는 Aviat 발주이력이 없어(04v2 재분석 결과 포함) 이 조합은 비교 대상이 될 수 없음.</t>
         </is>
       </c>
     </row>
@@ -936,7 +940,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>4GHz(WBX 근거) 또는 미상(계약서 텍스트 근거만 있음, 발주이력 없음)</t>
+          <t>8GHz 자체는 Aviat 자료에도 존재하나, 6+0 배수를 시사하는 발주이력 근거가 확인되지 않음(04v2 확인필요 시트 참조)</t>
         </is>
       </c>
       <c r="C11" s="3" t="n"/>
@@ -959,14 +963,14 @@
           <t>Ceragon 매입가 미제공</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>아니오</t>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>아니오(근거 없음)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Aviat 6+0 구성의 발주이력 근거는 4GHz 대역(WBX) 위주이며 8GHz 대역 자체 수량 근거가 없음(계약서 텍스트로 존재만 확인). Ceragon은 8GHz/Non_SD 데이터가 있으나 대역이 달라 동일 링크 총액으로 합산 비교하지 않음.</t>
+          <t>대역(8GHz)은 Aviat·Ceragon 양측 자료에 모두 존재하므로 '대역이 겹치지 않는다'고 표현하지 않는다. 다만 6+0 구성 자체를 시사하는 Aviat 발주이력이 없어(04v2 재분석 결과 포함) 이 조합은 비교 대상이 될 수 없음.</t>
         </is>
       </c>
     </row>
@@ -978,7 +982,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>4GHz(WBX 근거) 또는 미상(계약서 텍스트 근거만 있음, 발주이력 없음)</t>
+          <t>11GHz 자체는 Aviat 자료에도 존재하나, 6+0 배수를 시사하는 발주이력 근거가 확인되지 않음(04v2 확인필요 시트 참조)</t>
         </is>
       </c>
       <c r="C12" s="3" t="n"/>
@@ -1001,14 +1005,14 @@
           <t>Ceragon 매입가 미제공</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>아니오</t>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>아니오(근거 없음)</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Aviat 6+0 구성의 발주이력 근거는 4GHz 대역(WBX) 위주이며 11GHz 대역 자체 수량 근거가 없음(계약서 텍스트로 존재만 확인). Ceragon은 11GHz/SD 데이터가 있으나 대역이 달라 동일 링크 총액으로 합산 비교하지 않음.</t>
+          <t>대역(11GHz)은 Aviat·Ceragon 양측 자료에 모두 존재하므로 '대역이 겹치지 않는다'고 표현하지 않는다. 다만 6+0 구성 자체를 시사하는 Aviat 발주이력이 없어(04v2 재분석 결과 포함) 이 조합은 비교 대상이 될 수 없음.</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1024,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>4GHz(WBX 근거) 또는 미상(계약서 텍스트 근거만 있음, 발주이력 없음)</t>
+          <t>11GHz 자체는 Aviat 자료에도 존재하나, 6+0 배수를 시사하는 발주이력 근거가 확인되지 않음(04v2 확인필요 시트 참조)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n"/>
@@ -1043,14 +1047,14 @@
           <t>Ceragon 매입가 미제공</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>아니오</t>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>아니오(근거 없음)</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Aviat 6+0 구성의 발주이력 근거는 4GHz 대역(WBX) 위주이며 11GHz 대역 자체 수량 근거가 없음(계약서 텍스트로 존재만 확인). Ceragon은 11GHz/Non_SD 데이터가 있으나 대역이 달라 동일 링크 총액으로 합산 비교하지 않음.</t>
+          <t>대역(11GHz)은 Aviat·Ceragon 양측 자료에 모두 존재하므로 '대역이 겹치지 않는다'고 표현하지 않는다. 다만 6+0 구성 자체를 시사하는 Aviat 발주이력이 없어(04v2 재분석 결과 포함) 이 조합은 비교 대상이 될 수 없음.</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1066,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>4GHz(WBX 근거) 또는 미상(계약서 텍스트 근거만 있음, 발주이력 없음)</t>
+          <t>8GHz 자체는 Aviat 자료에도 존재하나, 8+0 배수를 시사하는 발주이력 근거가 확인되지 않음(04v2 확인필요 시트 참조)</t>
         </is>
       </c>
       <c r="C14" s="3" t="n"/>
@@ -1085,14 +1089,14 @@
           <t>Ceragon 매입가 미제공</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>아니오</t>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>아니오(근거 없음)</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Aviat 8+0 구성의 발주이력 근거는 4GHz 대역(WBX) 위주이며 8GHz 대역 자체 수량 근거가 없음(계약서 텍스트로 존재만 확인). Ceragon은 8GHz/SD 데이터가 있으나 대역이 달라 동일 링크 총액으로 합산 비교하지 않음.</t>
+          <t>대역(8GHz)은 Aviat·Ceragon 양측 자료에 모두 존재하므로 '대역이 겹치지 않는다'고 표현하지 않는다. 다만 8+0 구성 자체를 시사하는 Aviat 발주이력이 없어(04v2 재분석 결과 포함) 이 조합은 비교 대상이 될 수 없음.</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1108,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>4GHz(WBX 근거) 또는 미상(계약서 텍스트 근거만 있음, 발주이력 없음)</t>
+          <t>8GHz 자체는 Aviat 자료에도 존재하나, 8+0 배수를 시사하는 발주이력 근거가 확인되지 않음(04v2 확인필요 시트 참조)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n"/>
@@ -1127,14 +1131,14 @@
           <t>Ceragon 매입가 미제공</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>아니오</t>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>아니오(근거 없음)</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Aviat 8+0 구성의 발주이력 근거는 4GHz 대역(WBX) 위주이며 8GHz 대역 자체 수량 근거가 없음(계약서 텍스트로 존재만 확인). Ceragon은 8GHz/Non_SD 데이터가 있으나 대역이 달라 동일 링크 총액으로 합산 비교하지 않음.</t>
+          <t>대역(8GHz)은 Aviat·Ceragon 양측 자료에 모두 존재하므로 '대역이 겹치지 않는다'고 표현하지 않는다. 다만 8+0 구성 자체를 시사하는 Aviat 발주이력이 없어(04v2 재분석 결과 포함) 이 조합은 비교 대상이 될 수 없음.</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1150,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>4GHz(WBX 근거) 또는 미상(계약서 텍스트 근거만 있음, 발주이력 없음)</t>
+          <t>11GHz 자체는 Aviat 자료에도 존재하나, 8+0 배수를 시사하는 발주이력 근거가 확인되지 않음(04v2 확인필요 시트 참조)</t>
         </is>
       </c>
       <c r="C16" s="3" t="n"/>
@@ -1169,14 +1173,14 @@
           <t>Ceragon 매입가 미제공</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>아니오</t>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>아니오(근거 없음)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Aviat 8+0 구성의 발주이력 근거는 4GHz 대역(WBX) 위주이며 11GHz 대역 자체 수량 근거가 없음(계약서 텍스트로 존재만 확인). Ceragon은 11GHz/SD 데이터가 있으나 대역이 달라 동일 링크 총액으로 합산 비교하지 않음.</t>
+          <t>대역(11GHz)은 Aviat·Ceragon 양측 자료에 모두 존재하므로 '대역이 겹치지 않는다'고 표현하지 않는다. 다만 8+0 구성 자체를 시사하는 Aviat 발주이력이 없어(04v2 재분석 결과 포함) 이 조합은 비교 대상이 될 수 없음.</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1192,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>4GHz(WBX 근거) 또는 미상(계약서 텍스트 근거만 있음, 발주이력 없음)</t>
+          <t>11GHz 자체는 Aviat 자료에도 존재하나, 8+0 배수를 시사하는 발주이력 근거가 확인되지 않음(04v2 확인필요 시트 참조)</t>
         </is>
       </c>
       <c r="C17" s="3" t="n"/>
@@ -1211,14 +1215,14 @@
           <t>Ceragon 매입가 미제공</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>아니오</t>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>아니오(근거 없음)</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Aviat 8+0 구성의 발주이력 근거는 4GHz 대역(WBX) 위주이며 11GHz 대역 자체 수량 근거가 없음(계약서 텍스트로 존재만 확인). Ceragon은 11GHz/Non_SD 데이터가 있으나 대역이 달라 동일 링크 총액으로 합산 비교하지 않음.</t>
+          <t>대역(11GHz)은 Aviat·Ceragon 양측 자료에 모두 존재하므로 '대역이 겹치지 않는다'고 표현하지 않는다. 다만 8+0 구성 자체를 시사하는 Aviat 발주이력이 없어(04v2 재분석 결과 포함) 이 조합은 비교 대상이 될 수 없음.</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1503,7 @@
         <f>D2-H2</f>
         <v/>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="6">
         <f>IF(D2=0,0,I2/D2)</f>
         <v/>
       </c>
@@ -1548,7 +1552,7 @@
         <f>D3-H3</f>
         <v/>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="6">
         <f>IF(D3=0,0,I3/D3)</f>
         <v/>
       </c>
@@ -1597,7 +1601,7 @@
         <f>D4-H4</f>
         <v/>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="6">
         <f>IF(D4=0,0,I4/D4)</f>
         <v/>
       </c>
@@ -1624,8 +1628,8 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1696,17 +1700,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>데이터 부족(4GHz 위주)</t>
+          <t>8GHz/11GHz 대역 자체는 존재(04v2 IAP3 재분석). 2+0/4+0은 유력/참고 후보 수준 근거 있으나 완성 BoM 미확정, 6+0/8+0은 근거 자체 없음</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>8GHz/11GHz 매트릭스 존재</t>
+          <t>8GHz/11GHz 매트릭스 존재(2+0~8+0 전 구성)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>구성총액_비교 시트 전체가 '비교불가' - 근거 부족</t>
+          <t>구성총액_비교 시트: 2+0/4+0(8·11GHz)은 '보류'(대역은 겹침, Aviat 미확정), 6+0/8+0(8·11GHz) 및 4GHz 전 구성(WBX/CTR 앵커)은 '비교불가' - 자세한 사유는 구성총액_비교/비교불가 시트 참조</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1777,7 @@
       <c r="C2" s="3" t="n">
         <v>123500</v>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Ceragon 매입가 미제공</t>
         </is>
@@ -1798,7 +1802,7 @@
       <c r="C3" s="3" t="n">
         <v>70000</v>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Ceragon 매입가 미제공</t>
         </is>
@@ -1823,7 +1827,7 @@
       <c r="C4" s="3" t="n">
         <v>285000</v>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Ceragon 매입가 미제공</t>
         </is>
@@ -1846,7 +1850,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n"/>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Ceragon 매입가 미제공</t>
         </is>
@@ -1869,7 +1873,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n"/>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Ceragon 매입가 미제공</t>
         </is>
@@ -1892,7 +1896,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Ceragon 매입가 미제공</t>
         </is>
@@ -1915,7 +1919,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n"/>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Ceragon 매입가 미제공</t>
         </is>
@@ -1938,12 +1942,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1971,204 +1975,136 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Aviat(4GHz 근거) vs Ceragon(8GHz)</t>
+          <t>Aviat(WBX/CTR 텍스트 앵커, 4GHz 위주) vs Ceragon(4GHz)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>동일 주파수 대역 기준 데이터가 양측 모두에 존재하지 않아 구성 총액 비교 불가</t>
+          <t>Ceragon 제공 자료에 4GHz 대역 수량 매트릭스 자체가 없음(라이선스 단가 일부 제외). 이는 Ceragon 쪽 4GHz 데이터 부재가 원인이며, Aviat·Ceragon 대역이 전반적으로 겹치지 않는다는 뜻은 아니다(8GHz/11GHz는 양측에 모두 존재 - 구성총액_비교 시트 참조).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2+0</t>
+          <t>4+0</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Aviat(4GHz 근거) vs Ceragon(11GHz)</t>
+          <t>Aviat(WBX/CTR 텍스트 앵커, 4GHz 위주) vs Ceragon(4GHz)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>동일 주파수 대역 기준 데이터가 양측 모두에 존재하지 않아 구성 총액 비교 불가</t>
+          <t>Ceragon 제공 자료에 4GHz 대역 수량 매트릭스 자체가 없음(라이선스 단가 일부 제외). 이는 Ceragon 쪽 4GHz 데이터 부재가 원인이며, Aviat·Ceragon 대역이 전반적으로 겹치지 않는다는 뜻은 아니다(8GHz/11GHz는 양측에 모두 존재 - 구성총액_비교 시트 참조).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2+0</t>
+          <t>6+0</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Aviat(자체 4GHz) vs Ceragon(4GHz)</t>
+          <t>Aviat(8GHz) vs Ceragon(8GHz)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Ceragon 제공 자료에 4GHz 대역 수량 매트릭스 자체가 없음(라이선스 단가 일부 제외)</t>
+          <t>8GHz 대역 자체는 Aviat 자료에도 존재하나(04v2 참조), 6+0 배수를 시사하는 Aviat 발주이력 근거가 전혀 확인되지 않음(대역 불일치가 아니라 이 배수의 근거 부족 - 공급사 확인 필요).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>4+0</t>
+          <t>6+0</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Aviat(4GHz 근거) vs Ceragon(8GHz)</t>
+          <t>Aviat(11GHz) vs Ceragon(11GHz)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>동일 주파수 대역 기준 데이터가 양측 모두에 존재하지 않아 구성 총액 비교 불가</t>
+          <t>11GHz 대역 자체는 Aviat 자료에도 존재하나(04v2 참조), 6+0 배수를 시사하는 Aviat 발주이력 근거가 전혀 확인되지 않음(대역 불일치가 아니라 이 배수의 근거 부족 - 공급사 확인 필요).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>4+0</t>
+          <t>6+0</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Aviat(4GHz 근거) vs Ceragon(11GHz)</t>
+          <t>Aviat(WBX/CTR 텍스트 앵커, 4GHz 위주) vs Ceragon(4GHz)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>동일 주파수 대역 기준 데이터가 양측 모두에 존재하지 않아 구성 총액 비교 불가</t>
+          <t>Ceragon 제공 자료에 4GHz 대역 수량 매트릭스 자체가 없음(라이선스 단가 일부 제외). 이는 Ceragon 쪽 4GHz 데이터 부재가 원인이며, Aviat·Ceragon 대역이 전반적으로 겹치지 않는다는 뜻은 아니다(8GHz/11GHz는 양측에 모두 존재 - 구성총액_비교 시트 참조).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>4+0</t>
+          <t>8+0</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Aviat(자체 4GHz) vs Ceragon(4GHz)</t>
+          <t>Aviat(8GHz) vs Ceragon(8GHz)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Ceragon 제공 자료에 4GHz 대역 수량 매트릭스 자체가 없음(라이선스 단가 일부 제외)</t>
+          <t>8GHz 대역 자체는 Aviat 자료에도 존재하나(04v2 참조), 8+0 배수를 시사하는 Aviat 발주이력 근거가 전혀 확인되지 않음(대역 불일치가 아니라 이 배수의 근거 부족 - 공급사 확인 필요).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>6+0</t>
+          <t>8+0</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Aviat(4GHz 근거) vs Ceragon(8GHz)</t>
+          <t>Aviat(11GHz) vs Ceragon(11GHz)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>동일 주파수 대역 기준 데이터가 양측 모두에 존재하지 않아 구성 총액 비교 불가</t>
+          <t>11GHz 대역 자체는 Aviat 자료에도 존재하나(04v2 참조), 8+0 배수를 시사하는 Aviat 발주이력 근거가 전혀 확인되지 않음(대역 불일치가 아니라 이 배수의 근거 부족 - 공급사 확인 필요).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>6+0</t>
+          <t>8+0</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Aviat(4GHz 근거) vs Ceragon(11GHz)</t>
+          <t>Aviat(WBX/CTR 텍스트 앵커, 4GHz 위주) vs Ceragon(4GHz)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>동일 주파수 대역 기준 데이터가 양측 모두에 존재하지 않아 구성 총액 비교 불가</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>6+0</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Aviat(자체 4GHz) vs Ceragon(4GHz)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Ceragon 제공 자료에 4GHz 대역 수량 매트릭스 자체가 없음(라이선스 단가 일부 제외)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>8+0</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Aviat(4GHz 근거) vs Ceragon(8GHz)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>동일 주파수 대역 기준 데이터가 양측 모두에 존재하지 않아 구성 총액 비교 불가</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>8+0</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Aviat(4GHz 근거) vs Ceragon(11GHz)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>동일 주파수 대역 기준 데이터가 양측 모두에 존재하지 않아 구성 총액 비교 불가</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>8+0</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Aviat(자체 4GHz) vs Ceragon(4GHz)</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Ceragon 제공 자료에 4GHz 대역 수량 매트릭스 자체가 없음(라이선스 단가 일부 제외)</t>
+          <t>Ceragon 제공 자료에 4GHz 대역 수량 매트릭스 자체가 없음(라이선스 단가 일부 제외). 이는 Ceragon 쪽 4GHz 데이터 부재가 원인이며, Aviat·Ceragon 대역이 전반적으로 겹치지 않는다는 뜻은 아니다(8GHz/11GHz는 양측에 모두 존재 - 구성총액_비교 시트 참조).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C13"/>
+  <autoFilter ref="A1:C9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2204,7 +2140,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Aviat: 8GHz/11GHz 대역 각각의 2+0/4+0/6+0/8+0 구성 표준 BoM 수량 회신(현재 4GHz만 발주이력 근거가 있어 Ceragon과 동일 대역 비교 불가).</t>
+          <t>Aviat: 8GHz/11GHz 2+0/4+0 구성에 대해 04v2 재분석(발주이력 기반)에서 식별된 유력/참고 후보 품목·수량이 실제 표준 BoM과 일치하는지 확인 회신 요청. 아울러 6+0/8+0 구성이 IAP3 계열(8/11GHz)에서 실제로 존재하는지, 존재한다면 표준 BoM 수량은 얼마인지 회신 요청(현재 발주이력에는 이 배수를 시사하는 근거가 전혀 없음).</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2223,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>개별 품목 단위 3건(SFP류)만 직접 비교 가능. 구성 총액(2+0~8+0) 단위 비교는 Aviat·Ceragon 양측이 신뢰할 만한 데이터를 갖는 공통 주파수 대역이 없어 전량 비교불가로 처리.</t>
+          <t>개별 품목 단위 3건(SFP류)은 직접 비교 가능. 구성 총액(2+0~8+0) 단위 비교는: (1) 8GHz/11GHz는 Aviat·Ceragon 양측 자료에 모두 존재함(대역은 겹침 - 04v2 IAP3 재분석 참조). (2) 다만 Aviat 측 8GHz/11GHz 2+0/4+0 후보는 04v2에서 유력/참고 후보 수준까지만 확인되고 완성된 표준 BoM으로 확정되지 않아, 구성 총액 단위의 전면 비교는 보류함. (3) 6+0/8+0은 그 배수를 시사하는 Aviat 발주이력 근거 자체가 없어 비교 불가. (4) Aviat의 4GHz(WBX/CTR 텍스트 앵커) 전 구성은 Ceragon 쪽에 4GHz 수량 자료 자체가 없어 비교 불가. 요컨대 '대역이 겹치지 않는다'가 아니라 'Aviat 완성 BoM 미확정으로 구성 총액 비교가 보류'된 상태다(자세한 내용은 구성총액_비교/ 비교불가 시트 참조).</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2259,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>협상에 즉시 활용 가능한 것은 개별 SFP 단가 비교뿐이며, 구성 단위 총액 비교를 위해서는 5·6단계에서 식별된 확인필요 사항(Aviat 8/11GHz 회신, Ceragon 4GHz 지원여부, Ceragon 매입가)이 먼저 해소되어야 함.</t>
+          <t>협상에 즉시 활용 가능한 것은 개별 SFP 단가 비교뿐이다. 구성 단위 총액 비교를 진행하려면 04v2에서 이미 유력 후보 수준까지 확인된 11GHz 2+0 핵심 품목(VR4 CHASSIS/ODU LOW·HIGH/FAN-CV/Mounting Bracket/Node License)부터 Aviat에 표준 BoM 회신을 요청해 확정하고, 8GHz/11GHz 4+0 및 6+0/8+0 배수 존재 여부까지 함께 확인받는 것이 다음 단계다(다른 확인필요 사항은 5·6단계 결과 및 이 파일 공급사확인사항 시트 참조).</t>
         </is>
       </c>
     </row>

--- a/output/07_Aviat_Ceragon_구성가격비교.xlsx
+++ b/output/07_Aviat_Ceragon_구성가격비교.xlsx
@@ -23,8 +23,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'판매가_비교'!$A$1:$E$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'매입가_비교'!$A$1:$E$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'비교불가'!$A$1:$C$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'공급사확인사항'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'요약'!$A$1:$B$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'공급사확인사항'!$A$1:$B$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'요약'!$A$1:$B$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -558,7 +558,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>8GHz 2+0: 04v2 재분석 결과 참고후보 21건만 확인(반복 관측으로 뒷받침되는 유력 후보 없음)</t>
+          <t>8GHz 2+0: 04v2 재분석 결과 참고후보 19건만 확인(반복 관측으로 뒷받침되는 유력 후보 없음)</t>
         </is>
       </c>
       <c r="C2" s="3" t="n"/>
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>8GHz 2+0: 04v2 재분석 결과 참고후보 21건만 확인(반복 관측으로 뒷받침되는 유력 후보 없음)</t>
+          <t>8GHz 2+0: 04v2 재분석 결과 참고후보 19건만 확인(반복 관측으로 뒷받침되는 유력 후보 없음)</t>
         </is>
       </c>
       <c r="C3" s="3" t="n"/>
@@ -642,7 +642,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>11GHz 2+0: 04v2 재분석 결과 유력후보 6건/참고후보 39건(표준 BoM 확정 아님)</t>
+          <t>11GHz 2+0: 04v2 재분석 결과 유력후보 6건/참고후보 35건(표준 BoM 확정 아님)</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -674,7 +674,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>대역(11GHz)은 Aviat·Ceragon 양측에 모두 존재함(대역 자체는 겹침). 04v2 재분석에서 2+0 구성의 핵심 품목 6건이 '유력 후보' 수준까지 확인되었으나(반복 관측 비율 안정), 전체 품목(45건) 중 다수는 아직 참고 후보 단계이고 완성된 표준 BoM으로 확정되지 않아, 구성 총액 단위의 전면 비교는 보류한다. 왼쪽 '판매총액' 값은 유력후보 품목만의 부분 합계(참고용)이며 Ceragon 쪽 전체 품목 총액과 직접 비교 가능한 값이 아니다.</t>
+          <t>대역(11GHz)은 Aviat·Ceragon 양측에 모두 존재함(대역 자체는 겹침). 04v2 재분석에서 2+0 구성의 핵심 품목 6건이 '유력 후보' 수준까지 확인되었으나(반복 관측 비율 안정), 전체 품목(41건) 중 다수는 아직 참고 후보 단계이고 완성된 표준 BoM으로 확정되지 않아, 구성 총액 단위의 전면 비교는 보류한다. 왼쪽 '판매총액' 값은 유력후보 품목만의 부분 합계(참고용)이며 Ceragon 쪽 전체 품목 총액과 직접 비교 가능한 값이 아니다.</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>11GHz 2+0: 04v2 재분석 결과 유력후보 6건/참고후보 39건(표준 BoM 확정 아님)</t>
+          <t>11GHz 2+0: 04v2 재분석 결과 유력후보 6건/참고후보 35건(표준 BoM 확정 아님)</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>대역(11GHz)은 Aviat·Ceragon 양측에 모두 존재함(대역 자체는 겹침). 04v2 재분석에서 2+0 구성의 핵심 품목 6건이 '유력 후보' 수준까지 확인되었으나(반복 관측 비율 안정), 전체 품목(45건) 중 다수는 아직 참고 후보 단계이고 완성된 표준 BoM으로 확정되지 않아, 구성 총액 단위의 전면 비교는 보류한다. 왼쪽 '판매총액' 값은 유력후보 품목만의 부분 합계(참고용)이며 Ceragon 쪽 전체 품목 총액과 직접 비교 가능한 값이 아니다.</t>
+          <t>대역(11GHz)은 Aviat·Ceragon 양측에 모두 존재함(대역 자체는 겹침). 04v2 재분석에서 2+0 구성의 핵심 품목 6건이 '유력 후보' 수준까지 확인되었으나(반복 관측 비율 안정), 전체 품목(41건) 중 다수는 아직 참고 후보 단계이고 완성된 표준 BoM으로 확정되지 않아, 구성 총액 단위의 전면 비교는 보류한다. 왼쪽 '판매총액' 값은 유력후보 품목만의 부분 합계(참고용)이며 Ceragon 쪽 전체 품목 총액과 직접 비교 가능한 값이 아니다.</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>11GHz 4+0: 04v2 재분석 결과 참고후보 17건만 확인(반복 관측으로 뒷받침되는 유력 후보 없음)</t>
+          <t>11GHz 4+0: 04v2 재분석 결과 참고후보 13건만 확인(반복 관측으로 뒷받침되는 유력 후보 없음)</t>
         </is>
       </c>
       <c r="C8" s="3" t="n"/>
@@ -856,7 +856,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11GHz 4+0: 04v2 재분석 결과 참고후보 17건만 확인(반복 관측으로 뒷받침되는 유력 후보 없음)</t>
+          <t>11GHz 4+0: 04v2 재분석 결과 참고후보 13건만 확인(반복 관측으로 뒷받침되는 유력 후보 없음)</t>
         </is>
       </c>
       <c r="C9" s="3" t="n"/>
@@ -2115,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Aviat: 8GHz/11GHz 2+0/4+0 구성에 대해 04v2 재분석(발주이력 기반)에서 식별된 유력/참고 후보 품목·수량이 실제 표준 BoM과 일치하는지 확인 회신 요청. 아울러 6+0/8+0 구성이 IAP3 계열(8/11GHz)에서 실제로 존재하는지, 존재한다면 표준 BoM 수량은 얼마인지 회신 요청(현재 발주이력에는 이 배수를 시사하는 근거가 전혀 없음).</t>
+          <t>[1순위] Aviat: 8GHz IAP3 기준 2+0/4+0 대표 표준 구성(수량 포함)은 무엇인가? - 04v2에서 8GHz 2+0은 EVT-003(2025-06-27) 1건, 8GHz 4+0은 EVT-013(2026-04-27) 1건에서 VR4 CHASSIS/ODU LOW·HIGH/FAN-CV/License/Mounting Bracket/Hybrid가 각각 정확히 동일 비율로 함께 관측됨(관측횟수 1건, 아직 독립 반복 없음) - 이 조합이 맞는지 확인 요청.</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Ceragon: 4GHz 대역 지원 여부 및 지원 시 구성별 BoM/단가 제공.</t>
+          <t>[2순위] Aviat: 11GHz IAP3 기준 2+0/4+0 대표 표준 구성(수량 포함)은 무엇인가? - 04v2에서 11GHz 2+0은 EVT-007·EVT-010 두 독립 이벤트에서 VR4 CHASSIS/ODU LOW·HIGH/FAN-CV/Node License/Mounting Bracket 6개 품목이 반복 비율 1.00으로 확인되어 '유력 후보'로 분류함(가장 근거가 뚜렷함) - 이 조합의 정확성 확인 요청. 11GHz 4+0은 EVT-008 1건뿐이고 품목별 비율이 엇갈려(Chassis/Fan/License는 0.5, ODU/Modem은 1.0) 1개의 4채널 링크인지 2개의 2채널 링크가 섞인 것인지 불명확 - 확인 필요.</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Ceragon: '매입가'(KT 조달원가) 별도 제공 여부 - 현재 자료는 단가(공급가)만 존재.</t>
+          <t>[3순위] Aviat: VR4 적용 조건과 VR10 적용 조건은 무엇인가? - 두 계열이 언제 각각 선택되는지 (용량/거리/사이트 규모 등 기준) 발주이력만으로는 판단할 수 없음.</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Ceragon: 6GHz 대역 'Configuration SW Package' 라이선스가 실제 하드웨어 구성과 어떻게 연결되는지(현재 수량 매트릭스 공란) 확인.</t>
+          <t>[4순위] Aviat: WBX와 IAP3(VR4/VR10) 계열의 관계는 무엇인가? - 서로 대체 가능한 다른 세대 제품군인지, 용도가 구분된 별도 제품군인지, 필수/선택 여부 확인 요청.</t>
         </is>
       </c>
     </row>
@@ -2180,12 +2180,62 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>[5순위] Aviat: 6+0/8+0 구성이 실제로 공급 가능한가? - 계약품목·발주이력 어디에서도 6+0 표기 자체가 없고(2+0), 8+0은 IAP3 계열(8/11GHz)에서 발주 근거가 전혀 없음(WBX 계열 4GHz 8채널 표기만 확정) - 실제 공급 가능 여부와 가능하다면 표준 BoM 확인 요청.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Aviat: 213종 계약품목 전체에 대한 2+0/4+0/6+0/8+0 수량 기재 표준BoM 양식 회신(위 5개 질문보다 우선순위는 낮으나 여전히 필요).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Ceragon: 4GHz 대역 지원 여부 및 지원 시 구성별 BoM/단가 제공.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Ceragon: '매입가'(KT 조달원가) 별도 제공 여부 - 현재 자료는 단가(공급가)만 존재.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Ceragon: 6GHz 대역 'Configuration SW Package' 라이선스가 실제 하드웨어 구성과 어떻게 연결되는지(현재 수량 매트릭스 공란) 확인.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>직접대응_품목 3건(SFP류)의 정확한 온도/거리 사양 일치 여부 재확인.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:B11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2196,10 +2246,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -2218,53 +2268,65 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>비교 가능 범위</t>
+          <t>현재 단계(돈현님 피드백 반영, 2026-09-04)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>개별 품목 단위 3건(SFP류)은 직접 비교 가능. 구성 총액(2+0~8+0) 단위 비교는: (1) 8GHz/11GHz는 Aviat·Ceragon 양측 자료에 모두 존재함(대역은 겹침 - 04v2 IAP3 재분석 참조). (2) 다만 Aviat 측 8GHz/11GHz 2+0/4+0 후보는 04v2에서 유력/참고 후보 수준까지만 확인되고 완성된 표준 BoM으로 확정되지 않아, 구성 총액 단위의 전면 비교는 보류함. (3) 6+0/8+0은 그 배수를 시사하는 Aviat 발주이력 근거 자체가 없어 비교 불가. (4) Aviat의 4GHz(WBX/CTR 텍스트 앵커) 전 구성은 Ceragon 쪽에 4GHz 수량 자료 자체가 없어 비교 불가. 요컨대 '대역이 겹치지 않는다'가 아니라 'Aviat 완성 BoM 미확정으로 구성 총액 비교가 보류'된 상태다(자세한 내용은 구성총액_비교/ 비교불가 시트 참조).</t>
+          <t>이 파일은 아직 '가격 비교 자료'가 아니라 'Aviat에 무엇을 확인해야 하는지 정리한 자료' 단계다. 8GHz/11GHz IAP3 구성 후보는 04v2에서 식별했지만 전부 유력/참고 후보이고 '표준 BoM 확정' 품목은 아직 0건이므로, 가격 총액 비교에 앞서 공급사확인사항 시트의 5개 우선 질문에 대한 회신이 먼저 필요하다.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>직접대응 3건 결과</t>
+          <t>비교 가능 범위</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SFP류 3건 모두 Ceragon 단가가 Aviat 판매가보다 낮게 나타남(구체 수치는 직접대응_품목 시트 참조). 단, 이는 공식 견적이 아니라 참고용 단가 비교이므로 협상 근거로 바로 사용하지 말 것.</t>
+          <t>개별 품목 단위 3건(SFP류)은 직접 비교 가능. 구성 총액(2+0~8+0) 단위 비교는: (1) 8GHz/11GHz는 Aviat·Ceragon 양측 자료에 모두 존재함(대역은 겹침 - 04v2 IAP3 재분석 참조). (2) 다만 Aviat 측 8GHz/11GHz 2+0/4+0 후보는 04v2에서 유력/참고 후보 수준까지만 확인되고 완성된 표준 BoM으로 확정되지 않아, 구성 총액 단위의 전면 비교는 보류함. (3) 6+0/8+0은 그 배수를 시사하는 Aviat 발주이력 근거 자체가 없어 비교 불가. (4) Aviat의 4GHz(WBX/CTR 텍스트 앵커) 전 구성은 Ceragon 쪽에 4GHz 수량 자료 자체가 없어 비교 불가. 요컨대 '대역이 겹치지 않는다'가 아니라 'Aviat 완성 BoM 미확정으로 구성 총액 비교가 보류'된 상태다(자세한 내용은 구성총액_비교/ 비교불가 시트 참조).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>가격축 원칙 준수</t>
+          <t>직접대응 3건 결과</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Ceragon 매입가가 없어 Aviat 매입가는 어떤 Ceragon 수치와도 비교하지 않았음('Ceragon 매입가 미제공'으로 명시). 판매가 비교만 수행.</t>
+          <t>SFP류 3건 모두 Ceragon 단가가 Aviat 판매가보다 낮게 나타남(구체 수치는 직접대응_품목 시트 참조). 단, 이는 공식 견적이 아니라 참고용 단가 비교이므로 협상 근거로 바로 사용하지 말 것.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>가격축 원칙 준수</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Ceragon 매입가가 없어 Aviat 매입가는 어떤 Ceragon 수치와도 비교하지 않았음('Ceragon 매입가 미제공'으로 명시). 판매가 비교만 수행.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>핵심 결론</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>협상에 즉시 활용 가능한 것은 개별 SFP 단가 비교뿐이다. 구성 단위 총액 비교를 진행하려면 04v2에서 이미 유력 후보 수준까지 확인된 11GHz 2+0 핵심 품목(VR4 CHASSIS/ODU LOW·HIGH/FAN-CV/Mounting Bracket/Node License)부터 Aviat에 표준 BoM 회신을 요청해 확정하고, 8GHz/11GHz 4+0 및 6+0/8+0 배수 존재 여부까지 함께 확인받는 것이 다음 단계다(다른 확인필요 사항은 5·6단계 결과 및 이 파일 공급사확인사항 시트 참조).</t>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>협상에 즉시 활용 가능한 것은 개별 SFP 단가 비교뿐이다. 지금 병목은 가격이 아니라 BoM 확정이다: 11GHz 2+0은 독립된 2개 이벤트에서 반복 확인된 '유력 후보'(VR4 CHASSIS/ODU LOW·HIGH/FAN-CV/Mounting Bracket/Node License)까지 나왔고, 8GHz 2+0(EVT-003)과 8GHz 4+0(EVT-013)도 단일 이벤트지만 동일하게 깨끗한 패턴을 보였다(공급사확인사항 1·2순위 질문 참조). 다음 단계는 가격 비교가 아니라 이 3개 후보와 11GHz 4+0(EVT-008, 품목별 비율이 엇갈려 확인 필요)을 Aviat에 제시해 표준 BoM으로 확정받는 것이다(다른 확인필요 사항은 5·6단계 결과 및 이 파일 공급사확인사항 시트 참조).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B5"/>
+  <autoFilter ref="A1:B6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/07_Aviat_Ceragon_구성가격비교.xlsx
+++ b/output/07_Aviat_Ceragon_구성가격비교.xlsx
@@ -2285,7 +2285,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>개별 품목 단위 3건(SFP류)은 직접 비교 가능. 구성 총액(2+0~8+0) 단위 비교는: (1) 8GHz/11GHz는 Aviat·Ceragon 양측 자료에 모두 존재함(대역은 겹침 - 04v2 IAP3 재분석 참조). (2) 다만 Aviat 측 8GHz/11GHz 2+0/4+0 후보는 04v2에서 유력/참고 후보 수준까지만 확인되고 완성된 표준 BoM으로 확정되지 않아, 구성 총액 단위의 전면 비교는 보류함. (3) 6+0/8+0은 그 배수를 시사하는 Aviat 발주이력 근거 자체가 없어 비교 불가. (4) Aviat의 4GHz(WBX/CTR 텍스트 앵커) 전 구성은 Ceragon 쪽에 4GHz 수량 자료 자체가 없어 비교 불가. 요컨대 '대역이 겹치지 않는다'가 아니라 'Aviat 완성 BoM 미확정으로 구성 총액 비교가 보류'된 상태다(자세한 내용은 구성총액_비교/ 비교불가 시트 참조).</t>
+          <t>Aviat와 Ceragon은 8GHz 및 11GHz 대역이 공통으로 존재한다. 다만 Aviat의 구성방식별 완성 BoM이 아직 공식적으로 확인되지 않아 구성 총액 비교는 보류한다. 개별 품목 단위 3건(SFP류)은 직접 비교 가능. 세부적으로는: (1) 8GHz/11GHz 2+0/4+0 후보는 04v2에서 유력/참고 후보 수준까지만 확인되고 완성된 표준 BoM으로 확정되지 않아, 구성 총액 단위의 전면 비교는 보류함. (2) 6+0/8+0은 그 배수를 시사하는 Aviat 발주이력 근거 자체가 없어 비교 불가. (3) Aviat의 4GHz(WBX/CTR 텍스트 앵커) 전 구성은 Ceragon 쪽에 4GHz 수량 자료 자체가 없어 비교 불가(자세한 내용은 구성총액_비교/비교불가 시트 참조).</t>
         </is>
       </c>
     </row>

--- a/output/07_Aviat_Ceragon_구성가격비교.xlsx
+++ b/output/07_Aviat_Ceragon_구성가격비교.xlsx
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'판매가_비교'!$A$1:$E$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'매입가_비교'!$A$1:$E$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'비교불가'!$A$1:$C$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'공급사확인사항'!$A$1:$B$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'공급사확인사항'!$A$1:$B$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'요약'!$A$1:$B$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2115,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2230,12 +2230,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>Ceragon: 6GHz 'Configuration SW Package' 8개 품목(신규코드-R484~R491) 설명에 적힌 'Nnd-Activation' 표기가 2+0 SD=2nd부터 8+0 Non_SD=9nd까지 순차 증가하는데, 같은 라이선스 계열인 8GHz/11GHz용 8개 품목(R492~R499)은 전부 '2nd-Activation'으로 동일하다 - 6GHz 쪽만 값이 순차 증가하는 것은 원본 가격표 작성 시 행 복사 과정에서 번호가 밀린 것으로 보인다(2nd로 통일 여부 확인 필요, 6GHz 쪽 전체를 '2nd-Activation'으로 통일해야 하는지 확인 요청).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>직접대응_품목 3건(SFP류)의 정확한 온도/거리 사양 일치 여부 재확인.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B11"/>
+  <autoFilter ref="A1:B12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/output/07_Aviat_Ceragon_구성가격비교.xlsx
+++ b/output/07_Aviat_Ceragon_구성가격비교.xlsx
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>9544236</v>
+        <v>19088472</v>
       </c>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>9544236</v>
+        <v>19088472</v>
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="2" t="inlineStr">

--- a/output/07_Aviat_Ceragon_구성가격비교.xlsx
+++ b/output/07_Aviat_Ceragon_구성가격비교.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'구성총액_비교'!$A$1:$J$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'품목구성_차이'!$A$1:$D$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'직접대응_품목'!$A$1:$K$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'직접대응_품목'!$A$1:$L$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'판매가_비교'!$A$1:$E$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'매입가_비교'!$A$1:$E$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'비교불가'!$A$1:$C$9</definedName>
@@ -49,7 +49,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +69,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -98,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -116,6 +121,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1391,20 +1399,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1415,50 +1424,55 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>신뢰도 등급</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Aviat K코드</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Aviat 품명</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Aviat 판매가</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Aviat 매입가</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Ceragon K코드</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Ceragon 품명</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Ceragon 단가(판매가/계약단가)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>판매가 차액</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>판매가 차이율</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -1470,46 +1484,51 @@
           <t>옥외(Outdoor)용 산업용 1G GbE SFP 광모듈</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>조건부 비교</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>K9198328</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Gigabit Ethernet SFP_Industrial_-40~+85℃_실외형</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>130000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>123500</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>K9183522</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> CER_SFP-GE-LX-EXT-TEMP </t>
         </is>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="I2" s="3" t="n">
         <v>104257.351</v>
       </c>
-      <c r="I2" s="3">
-        <f>D2-H2</f>
+      <c r="J2" s="3">
+        <f>E2-I2</f>
         <v/>
       </c>
-      <c r="J2" s="6">
-        <f>IF(D2=0,0,I2/D2)</f>
+      <c r="K2" s="6">
+        <f>IF(E2=0,0,J2/E2)</f>
         <v/>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>양측 모두 '옥외 Outdoor용 Optic Gbit Module' 설명이 동일. 온도사양은 Aviat -40~+85℃, Ceragon -30~+50℃로 약간 다름(확인 필요).</t>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>양측 모두 '옥외 Outdoor용 Optic Gbit Module' 설명이 동일. 온도사양은 Aviat -40~+85℃, Ceragon -30~+50℃로 등급 자체가 달라(산업용 vs 일반 옥외용 추정) 조건부로만 참고(확인 필요).</t>
         </is>
       </c>
     </row>
@@ -1519,46 +1538,51 @@
           <t>실내용 1G GbE SFP 광모듈</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>준직접 비교</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>K9210279</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>HAX_Gigabit Ethernet SFP</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>74180</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>70000</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>K9178770</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> CER_IP10-SFP-GE-LX </t>
         </is>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="I3" s="3" t="n">
         <v>58309.385</v>
       </c>
-      <c r="I3" s="3">
-        <f>D3-H3</f>
+      <c r="J3" s="3">
+        <f>E3-I3</f>
         <v/>
       </c>
-      <c r="J3" s="6">
-        <f>IF(D3=0,0,I3/D3)</f>
+      <c r="K3" s="6">
+        <f>IF(E3=0,0,J3/E3)</f>
         <v/>
       </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>양측 모두 실내형 1G Gigabit Ethernet SFP. 거리/파장 사양은 Aviat 자료에 명시되어 있지 않음(확인 필요).</t>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>양측 모두 실내형 1G Gigabit Ethernet SFP로 설명이 실질적으로 같아 3건 중 가장 근접한 매칭이다. 다만 거리/파장 사양이 Aviat 자료에 명시되어 있지 않아 완전 일치 확인은 아니다(확인 필요).</t>
         </is>
       </c>
     </row>
@@ -1568,51 +1592,56 @@
           <t>10G SFP+ 광모듈(참고용, 완전 동일 사양 아님)</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>참고 비교</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>K9198347</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>10Gigabit Ethernet SFP_Industrial_-40~+85℃_실외형</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>300000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>285000</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>K9197307</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>CER_10G SFP+ LR 1310nm 20km, SMF</t>
         </is>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="I4" s="3" t="n">
         <v>67104.84600000001</v>
       </c>
-      <c r="I4" s="3">
-        <f>D4-H4</f>
+      <c r="J4" s="3">
+        <f>E4-I4</f>
         <v/>
       </c>
-      <c r="J4" s="6">
-        <f>IF(D4=0,0,I4/D4)</f>
+      <c r="K4" s="6">
+        <f>IF(E4=0,0,J4/E4)</f>
         <v/>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Aviat 품목은 산업용/실외 등급(-40~+85℃)이나 Ceragon 품목은 실외 등급 명시가 없어 완전히 동일한 사양은 아님 - 참고용 비교(확인 필요).</t>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Aviat 품목은 산업용/실외 등급(-40~+85℃)이나 Ceragon 품목은 실외 등급 명시가 없고 장거리(LR, 20km) 사양 - Aviat가 실제로 장거리 사양을 요구하는지도 불명확해 등급·거리 모두 완전히 동일한 사양은 아님 - 참고 수준 비교(확인 필요).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K4"/>
+  <autoFilter ref="A1:L4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/output/07_Aviat_Ceragon_구성가격비교.xlsx
+++ b/output/07_Aviat_Ceragon_구성가격비교.xlsx
@@ -2179,7 +2179,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>[2순위] Aviat: 11GHz IAP3 기준 2+0/4+0 대표 표준 구성(수량 포함)은 무엇인가? - 04v2에서 11GHz 2+0은 EVT-007·EVT-010 두 독립 이벤트에서 VR4 CHASSIS/ODU LOW·HIGH/FAN-CV/Node License/Mounting Bracket 6개 품목이 반복 비율 1.00으로 확인되어 '유력 후보'로 분류함(가장 근거가 뚜렷함) - 이 조합의 정확성 확인 요청. 11GHz 4+0은 EVT-008 1건뿐이고 품목별 비율이 엇갈려(Chassis/Fan/License는 0.5, ODU/Modem은 1.0) 1개의 4채널 링크인지 2개의 2채널 링크가 섞인 것인지 불명확 - 확인 필요.</t>
+          <t>[2순위] Aviat: 11GHz IAP3 기준 2+0/4+0 대표 표준 구성(수량 포함)은 무엇인가? - 04v2에서 11GHz 2+0은 EVT-007·EVT-010 두 독립 이벤트에서 VR4 CHASSIS/ODU LOW·HIGH/FAN-CV/Node License/Mounting Bracket 6개 품목이 반복 비율 1.00으로 확인되어 '유력 후보'로 분류함(가장 근거가 뚜렷함) - 이 조합의 정확성 확인 요청. 11GHz 4+0은 EVT-008 1건뿐이고 품목별 비율이 엇갈려(Chassis/Fan/License는 0.5, ODU/Modem은 1.0) 1개의 4채널 링크인지 2개의 2채널 링크가 섞인 것인지 불명확 - 확인 필요. 추가로: 위 6개 품목이 발주이력상 각각 2개씩 관측됐는데, 이 '2'가 (a)링크 양단 사이트 합산 총수량인지 (b)사이트 1곳당 수량(따라서 링크 전체는 4개)인지 자체가 확인되지 않았다 - 14번 파일에서는 Ceragon 자료의 A/B국소 합산 관례를 적용해 (a)로 해석했으나(19,088,472원의 근거), 이는 정황상 가정일 뿐 Aviat 공식 확인이 아니므로 반드시 확인 요청.</t>
         </is>
       </c>
     </row>
